--- a/results/09-2025/beta/inputs-09-2025.xlsx
+++ b/results/09-2025/beta/inputs-09-2025.xlsx
@@ -33251,7 +33251,7 @@
         <v>1797.5</v>
       </c>
       <c r="S203" t="n">
-        <v>199.7</v>
+        <v>199.6</v>
       </c>
       <c r="T203" t="n">
         <v>0</v>
@@ -33308,7 +33308,7 @@
         <v>-1107.138</v>
       </c>
       <c r="AL203" t="n">
-        <v>-87.2566666666666</v>
+        <v>-87.2533333333332</v>
       </c>
       <c r="AM203" t="n">
         <v>-25.8066666666666</v>
@@ -33409,7 +33409,7 @@
         <v>1924.5</v>
       </c>
       <c r="S204" t="n">
-        <v>257.7</v>
+        <v>258.6</v>
       </c>
       <c r="T204" t="n">
         <v>0</v>
@@ -33466,7 +33466,7 @@
         <v>-1117.866</v>
       </c>
       <c r="AL204" t="n">
-        <v>-87.7966666666666</v>
+        <v>-87.8233333333332</v>
       </c>
       <c r="AM204" t="n">
         <v>-26.72</v>
@@ -33567,7 +33567,7 @@
         <v>1961.9</v>
       </c>
       <c r="S205" t="n">
-        <v>251</v>
+        <v>251.2</v>
       </c>
       <c r="T205" t="n">
         <v>0</v>
@@ -33624,7 +33624,7 @@
         <v>-1138.026</v>
       </c>
       <c r="AL205" t="n">
-        <v>-88.0833333333332</v>
+        <v>-88.1166666666666</v>
       </c>
       <c r="AM205" t="n">
         <v>-27.51</v>
@@ -33725,7 +33725,7 @@
         <v>2012.3</v>
       </c>
       <c r="S206" t="n">
-        <v>280</v>
+        <v>289.9</v>
       </c>
       <c r="T206" t="n">
         <v>0</v>
@@ -33782,7 +33782,7 @@
         <v>-1154.364</v>
       </c>
       <c r="AL206" t="n">
-        <v>-90.2333333333332</v>
+        <v>-90.5966666666666</v>
       </c>
       <c r="AM206" t="n">
         <v>-28.4</v>
@@ -33883,7 +33883,7 @@
         <v>2119.2</v>
       </c>
       <c r="S207" t="n">
-        <v>339.3</v>
+        <v>343.9</v>
       </c>
       <c r="T207" t="n">
         <v>0</v>
@@ -33940,7 +33940,7 @@
         <v>-1176.786</v>
       </c>
       <c r="AL207" t="n">
-        <v>-93.9066666666666</v>
+        <v>-94.4233333333332</v>
       </c>
       <c r="AM207" t="n">
         <v>-29.7066666666666</v>
@@ -34041,7 +34041,7 @@
         <v>2124.1</v>
       </c>
       <c r="S208" t="n">
-        <v>348.7</v>
+        <v>344.5</v>
       </c>
       <c r="T208" t="n">
         <v>0</v>
@@ -34098,7 +34098,7 @@
         <v>-1197.36</v>
       </c>
       <c r="AL208" t="n">
-        <v>-98.0133333333332</v>
+        <v>-98.3899999999999</v>
       </c>
       <c r="AM208" t="n">
         <v>-31.7766666666666</v>
@@ -34199,7 +34199,7 @@
         <v>2193.1</v>
       </c>
       <c r="S209" t="n">
-        <v>374</v>
+        <v>357.9</v>
       </c>
       <c r="T209" t="n">
         <v>0</v>
@@ -34256,7 +34256,7 @@
         <v>-1220.328</v>
       </c>
       <c r="AL209" t="n">
-        <v>-102.823333333333</v>
+        <v>-102.663333333333</v>
       </c>
       <c r="AM209" t="n">
         <v>-35.4366666666666</v>
@@ -34357,7 +34357,7 @@
         <v>2285.3</v>
       </c>
       <c r="S210" t="n">
-        <v>385</v>
+        <v>379.6</v>
       </c>
       <c r="T210" t="n">
         <v>0</v>
@@ -34414,7 +34414,7 @@
         <v>-1253.778</v>
       </c>
       <c r="AL210" t="n">
-        <v>-109.076666666667</v>
+        <v>-108.736666666667</v>
       </c>
       <c r="AM210" t="n">
         <v>-39.2</v>
@@ -34515,7 +34515,7 @@
         <v>2353.3</v>
       </c>
       <c r="S211" t="n">
-        <v>425.6</v>
+        <v>417.1</v>
       </c>
       <c r="T211" t="n">
         <v>0</v>
@@ -34572,7 +34572,7 @@
         <v>-1296.738</v>
       </c>
       <c r="AL211" t="n">
-        <v>-116.41</v>
+        <v>-115.786666666667</v>
       </c>
       <c r="AM211" t="n">
         <v>-42.12</v>
@@ -34673,7 +34673,7 @@
         <v>2270.7</v>
       </c>
       <c r="S212" t="n">
-        <v>416.9</v>
+        <v>402.2</v>
       </c>
       <c r="T212" t="n">
         <v>4.73961878202226</v>
@@ -34730,7 +34730,7 @@
         <v>-1316.634</v>
       </c>
       <c r="AL212" t="n">
-        <v>-123.41</v>
+        <v>-122.296666666667</v>
       </c>
       <c r="AM212" t="n">
         <v>-45.3033333333333</v>
@@ -34831,7 +34831,7 @@
         <v>2266.1</v>
       </c>
       <c r="S213" t="n">
-        <v>419.3</v>
+        <v>406.9</v>
       </c>
       <c r="T213" t="n">
         <v>7.97769868483218</v>
@@ -34888,7 +34888,7 @@
         <v>-1329.654</v>
       </c>
       <c r="AL213" t="n">
-        <v>-129.656666666667</v>
+        <v>-128.13</v>
       </c>
       <c r="AM213" t="n">
         <v>-48.92</v>
@@ -34989,7 +34989,7 @@
         <v>2245.5</v>
       </c>
       <c r="S214" t="n">
-        <v>419.2</v>
+        <v>434.3</v>
       </c>
       <c r="T214" t="n">
         <v>30.340947133778</v>
@@ -35046,7 +35046,7 @@
         <v>-1342.134</v>
       </c>
       <c r="AL214" t="n">
-        <v>-137.213333333333</v>
+        <v>-136.19</v>
       </c>
       <c r="AM214" t="n">
         <v>-52.5999999999999</v>
@@ -35147,7 +35147,7 @@
         <v>2236.1</v>
       </c>
       <c r="S215" t="n">
-        <v>415.5</v>
+        <v>429.4</v>
       </c>
       <c r="T215" t="n">
         <v>46.2453234375524</v>
@@ -35204,7 +35204,7 @@
         <v>-1347.348</v>
       </c>
       <c r="AL215" t="n">
-        <v>-144.406666666667</v>
+        <v>-143.85</v>
       </c>
       <c r="AM215" t="n">
         <v>-55.9899999999999</v>
@@ -35305,7 +35305,7 @@
         <v>2270.3</v>
       </c>
       <c r="S216" t="n">
-        <v>428.4</v>
+        <v>451.9</v>
       </c>
       <c r="T216" t="n">
         <v>62.0712654345618</v>
@@ -35362,7 +35362,7 @@
         <v>-1357.608</v>
       </c>
       <c r="AL216" t="n">
-        <v>-150.096666666666</v>
+        <v>-150.293333333333</v>
       </c>
       <c r="AM216" t="n">
         <v>-58.8866666666666</v>
@@ -35463,7 +35463,7 @@
         <v>2301.1</v>
       </c>
       <c r="S217" t="n">
-        <v>442.7</v>
+        <v>464.8</v>
       </c>
       <c r="T217" t="n">
         <v>68.3121900998493</v>
@@ -35520,7 +35520,7 @@
         <v>-1367.988</v>
       </c>
       <c r="AL217" t="n">
-        <v>-156.486666666666</v>
+        <v>-157.413333333333</v>
       </c>
       <c r="AM217" t="n">
         <v>-62.0366666666666</v>
@@ -35621,7 +35621,7 @@
         <v>2325.5</v>
       </c>
       <c r="S218" t="n">
-        <v>472.3</v>
+        <v>459.9</v>
       </c>
       <c r="T218" t="n">
         <v>78.0145380046553</v>
@@ -35678,7 +35678,7 @@
         <v>-1373.712</v>
       </c>
       <c r="AL218" t="n">
-        <v>-162.896666666666</v>
+        <v>-163.08</v>
       </c>
       <c r="AM218" t="n">
         <v>-65.0899999999999</v>
@@ -35779,7 +35779,7 @@
         <v>2363.6</v>
       </c>
       <c r="S219" t="n">
-        <v>495.3</v>
+        <v>493.4</v>
       </c>
       <c r="T219" t="n">
         <v>85.4387215838714</v>
@@ -35836,7 +35836,7 @@
         <v>-1378.08</v>
       </c>
       <c r="AL219" t="n">
-        <v>-168.096666666666</v>
+        <v>-168.063333333333</v>
       </c>
       <c r="AM219" t="n">
         <v>-67.4566666666666</v>
@@ -35937,7 +35937,7 @@
         <v>2400.1</v>
       </c>
       <c r="S220" t="n">
-        <v>490.6</v>
+        <v>493.1</v>
       </c>
       <c r="T220" t="n">
         <v>79.6290028317487</v>
@@ -35994,7 +35994,7 @@
         <v>-1390.32</v>
       </c>
       <c r="AL220" t="n">
-        <v>-172.826666666666</v>
+        <v>-173.016666666666</v>
       </c>
       <c r="AM220" t="n">
         <v>-69.0033333333332</v>
@@ -36095,7 +36095,7 @@
         <v>2436.6</v>
       </c>
       <c r="S221" t="n">
-        <v>508.6</v>
+        <v>512.1</v>
       </c>
       <c r="T221" t="n">
         <v>71.1791672183253</v>
@@ -36152,7 +36152,7 @@
         <v>-1404.93</v>
       </c>
       <c r="AL221" t="n">
-        <v>-177.313333333333</v>
+        <v>-178.156666666666</v>
       </c>
       <c r="AM221" t="n">
         <v>-69.0299999999999</v>
@@ -36253,7 +36253,7 @@
         <v>2460.1</v>
       </c>
       <c r="S222" t="n">
-        <v>469.2</v>
+        <v>519.8</v>
       </c>
       <c r="T222" t="n">
         <v>73.9806362924226</v>
@@ -36310,7 +36310,7 @@
         <v>-1421.406</v>
       </c>
       <c r="AL222" t="n">
-        <v>-180.12</v>
+        <v>-182.83</v>
       </c>
       <c r="AM222" t="n">
         <v>-69.0199999999999</v>
@@ -36411,7 +36411,7 @@
         <v>2490.5</v>
       </c>
       <c r="S223" t="n">
-        <v>469.7</v>
+        <v>532.1</v>
       </c>
       <c r="T223" t="n">
         <v>88.3944428040623</v>
@@ -36468,7 +36468,7 @@
         <v>-1439.904</v>
       </c>
       <c r="AL223" t="n">
-        <v>-181.59</v>
+        <v>-186.663333333333</v>
       </c>
       <c r="AM223" t="n">
         <v>-69.6399999999999</v>
@@ -36524,7 +36524,7 @@
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.00612589701812283</v>
+        <v>0.00000741709325358109</v>
       </c>
       <c r="E224" t="n">
         <v>0.00774551207611962</v>
@@ -36536,7 +36536,7 @@
         <v>0.00774551207611962</v>
       </c>
       <c r="H224" t="n">
-        <v>0.0061860942661327</v>
+        <v>0.00794846274723726</v>
       </c>
       <c r="I224" t="n">
         <v>0.00573662843673683</v>
@@ -36551,7 +36551,7 @@
         <v>-0.3</v>
       </c>
       <c r="M224" t="n">
-        <v>1981.79316480871</v>
+        <v>1979.74532893704</v>
       </c>
       <c r="N224" t="n">
         <v>413.928976503306</v>
@@ -36563,7 +36563,7 @@
         <v>3310.58125327749</v>
       </c>
       <c r="Q224" t="n">
-        <v>4957.98141700098</v>
+        <v>4936.98141700098</v>
       </c>
       <c r="R224" t="n">
         <v>2509.69750395893</v>
@@ -36578,7 +36578,7 @@
         <v>182.677135911152</v>
       </c>
       <c r="V224" t="n">
-        <v>2397.246605</v>
+        <v>2384.246605</v>
       </c>
       <c r="W224" t="n">
         <v>220.142871865933</v>
@@ -36614,25 +36614,25 @@
         <v>0</v>
       </c>
       <c r="AH224" t="n">
-        <v>1913.05144709876</v>
+        <v>1917.08175833305</v>
       </c>
       <c r="AI224" t="n">
-        <v>331.423885770521</v>
+        <v>333.393574536235</v>
       </c>
       <c r="AJ224" t="n">
-        <v>-2806.95377004012</v>
+        <v>-2804.43377004012</v>
       </c>
       <c r="AK224" t="n">
         <v>-1457.24370047507</v>
       </c>
       <c r="AL224" t="n">
-        <v>-170.320821636094</v>
+        <v>-175.884154969427</v>
       </c>
       <c r="AM224" t="n">
         <v>-70.0759045303717</v>
       </c>
       <c r="AN224" t="n">
-        <v>2099.664136125</v>
+        <v>2096.739136125</v>
       </c>
       <c r="AO224" t="n">
         <v>187.029646169835</v>
@@ -36665,10 +36665,10 @@
         <v>0.28035</v>
       </c>
       <c r="AY224" t="n">
-        <v>1662.46660059722</v>
+        <v>1663.37342062494</v>
       </c>
       <c r="AZ224" t="n">
-        <v>288.300349298367</v>
+        <v>288.743529270653</v>
       </c>
     </row>
     <row r="225">
@@ -36709,7 +36709,7 @@
         <v>-0.3</v>
       </c>
       <c r="M225" t="n">
-        <v>1968.07266446852</v>
+        <v>2006.76290286156</v>
       </c>
       <c r="N225" t="n">
         <v>412.672286524193</v>
@@ -36721,7 +36721,7 @@
         <v>3341.68181349335</v>
       </c>
       <c r="Q225" t="n">
-        <v>5042.94089286239</v>
+        <v>5021.94089286239</v>
       </c>
       <c r="R225" t="n">
         <v>2535.4148309503</v>
@@ -36736,7 +36736,7 @@
         <v>182.5855495212</v>
       </c>
       <c r="V225" t="n">
-        <v>2389.612953025</v>
+        <v>2376.612953025</v>
       </c>
       <c r="W225" t="n">
         <v>223.324677586102</v>
@@ -36772,25 +36772,25 @@
         <v>0</v>
       </c>
       <c r="AH225" t="n">
-        <v>1948.88834267355</v>
+        <v>1952.97849763588</v>
       </c>
       <c r="AI225" t="n">
-        <v>334.618226049299</v>
+        <v>336.606986627065</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-2857.30467718361</v>
+        <v>-2852.26467718361</v>
       </c>
       <c r="AK225" t="n">
         <v>-1473.99748018911</v>
       </c>
       <c r="AL225" t="n">
-        <v>-167.455408351703</v>
+        <v>-173.43207501837</v>
       </c>
       <c r="AM225" t="n">
         <v>-70.2020895144117</v>
       </c>
       <c r="AN225" t="n">
-        <v>2139.60500055563</v>
+        <v>2133.75500055563</v>
       </c>
       <c r="AO225" t="n">
         <v>191.310198626708</v>
@@ -36823,10 +36823,10 @@
         <v>0.250425</v>
       </c>
       <c r="AY225" t="n">
-        <v>1698.95965269877</v>
+        <v>1700.78675759301</v>
       </c>
       <c r="AZ225" t="n">
-        <v>292.87127515946</v>
+        <v>293.761926261743</v>
       </c>
     </row>
     <row r="226">
@@ -36864,10 +36864,10 @@
         <v>21376.2657836858</v>
       </c>
       <c r="L226" t="n">
-        <v>-0.3</v>
+        <v>-0.24</v>
       </c>
       <c r="M226" t="n">
-        <v>1993.6706128644</v>
+        <v>2051.1056274537</v>
       </c>
       <c r="N226" t="n">
         <v>415.453341230767</v>
@@ -36879,7 +36879,7 @@
         <v>3373.66737243847</v>
       </c>
       <c r="Q226" t="n">
-        <v>5052.13406595246</v>
+        <v>5030.93734741117</v>
       </c>
       <c r="R226" t="n">
         <v>2559.05905860302</v>
@@ -36894,7 +36894,7 @@
         <v>182.806434344026</v>
       </c>
       <c r="V226" t="n">
-        <v>2443.10113879012</v>
+        <v>2429.80213879012</v>
       </c>
       <c r="W226" t="n">
         <v>226.552471112076</v>
@@ -36930,25 +36930,25 @@
         <v>0</v>
       </c>
       <c r="AH226" t="n">
-        <v>1984.27731219351</v>
+        <v>1988.42126832392</v>
       </c>
       <c r="AI226" t="n">
-        <v>339.018474932709</v>
+        <v>341.03338782625</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-2902.62788007784</v>
+        <v>-2896.30427385289</v>
       </c>
       <c r="AK226" t="n">
         <v>-1490.97271698393</v>
       </c>
       <c r="AL226" t="n">
-        <v>-164.524673360412</v>
+        <v>-169.998006693745</v>
       </c>
       <c r="AM226" t="n">
         <v>-70.4989706592125</v>
       </c>
       <c r="AN226" t="n">
-        <v>2168.9232067834</v>
+        <v>2160.0809317834</v>
       </c>
       <c r="AO226" t="n">
         <v>196.542004626925</v>
@@ -36981,10 +36981,10 @@
         <v>0.222075</v>
       </c>
       <c r="AY226" t="n">
-        <v>1737.87234794231</v>
+        <v>1740.63184296589</v>
       </c>
       <c r="AZ226" t="n">
-        <v>297.945132019319</v>
+        <v>299.289138522649</v>
       </c>
     </row>
     <row r="227">
@@ -37022,10 +37022,10 @@
         <v>21572.2581943785</v>
       </c>
       <c r="L227" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="M227" t="n">
-        <v>2014.55853875543</v>
+        <v>2076.17476099563</v>
       </c>
       <c r="N227" t="n">
         <v>415.4587988</v>
@@ -37037,7 +37037,7 @@
         <v>3403.4892424388</v>
       </c>
       <c r="Q227" t="n">
-        <v>5093.60604756935</v>
+        <v>5072.21076771607</v>
       </c>
       <c r="R227" t="n">
         <v>2583.69345621437</v>
@@ -37052,7 +37052,7 @@
         <v>183.16739246913</v>
       </c>
       <c r="V227" t="n">
-        <v>2458.97523945408</v>
+        <v>2445.67623945408</v>
       </c>
       <c r="W227" t="n">
         <v>229.826917122492</v>
@@ -37088,25 +37088,25 @@
         <v>0</v>
       </c>
       <c r="AH227" t="n">
-        <v>2021.42509670947</v>
+        <v>2025.63003733759</v>
       </c>
       <c r="AI227" t="n">
-        <v>342.387030980667</v>
+        <v>344.421964455726</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-2943.88815221442</v>
+        <v>-2936.25711240707</v>
       </c>
       <c r="AK227" t="n">
         <v>-1507.07504187264</v>
       </c>
       <c r="AL227" t="n">
-        <v>-161.649040873098</v>
+        <v>-166.659040873098</v>
       </c>
       <c r="AM227" t="n">
         <v>-70.9312170748502</v>
       </c>
       <c r="AN227" t="n">
-        <v>2180.01058566057</v>
+        <v>2168.17603566057</v>
       </c>
       <c r="AO227" t="n">
         <v>202.465560979486</v>
@@ -37139,10 +37139,10 @@
         <v>0.1953</v>
       </c>
       <c r="AY227" t="n">
-        <v>1770.21949470194</v>
+        <v>1773.92510136685</v>
       </c>
       <c r="AZ227" t="n">
-        <v>303.175713989969</v>
+        <v>304.977580525187</v>
       </c>
     </row>
     <row r="228">
@@ -37180,10 +37180,10 @@
         <v>21743.5753015667</v>
       </c>
       <c r="L228" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="M228" t="n">
-        <v>2032.16992725179</v>
+        <v>2096.66663787088</v>
       </c>
       <c r="N228" t="n">
         <v>419.294929243438</v>
@@ -37195,7 +37195,7 @@
         <v>3433.8730194392</v>
       </c>
       <c r="Q228" t="n">
-        <v>5135.47534824619</v>
+        <v>5113.879647048</v>
       </c>
       <c r="R228" t="n">
         <v>2606.14312342119</v>
@@ -37210,7 +37210,7 @@
         <v>182.984219689226</v>
       </c>
       <c r="V228" t="n">
-        <v>2476.59535062135</v>
+        <v>2463.29635062135</v>
       </c>
       <c r="W228" t="n">
         <v>233.148689902827</v>
@@ -37246,25 +37246,25 @@
         <v>0</v>
       </c>
       <c r="AH228" t="n">
-        <v>2057.05111546849</v>
+        <v>2061.30465790122</v>
       </c>
       <c r="AI228" t="n">
-        <v>348.018295779852</v>
+        <v>350.086697956147</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-2985.41515004682</v>
+        <v>-2976.46442920816</v>
       </c>
       <c r="AK228" t="n">
         <v>-1522.262673167</v>
       </c>
       <c r="AL228" t="n">
-        <v>-158.275599146159</v>
+        <v>-162.502265812825</v>
       </c>
       <c r="AM228" t="n">
         <v>-71.4140243978244</v>
       </c>
       <c r="AN228" t="n">
-        <v>2197.86405342537</v>
+        <v>2185.96222842537</v>
       </c>
       <c r="AO228" t="n">
         <v>205.391870037787</v>
@@ -37297,10 +37297,10 @@
         <v>0.171675</v>
       </c>
       <c r="AY228" t="n">
-        <v>1802.61942008513</v>
+        <v>1806.37525376969</v>
       </c>
       <c r="AZ228" t="n">
-        <v>306.909456242069</v>
+        <v>308.733533294667</v>
       </c>
     </row>
     <row r="229">
@@ -37338,10 +37338,10 @@
         <v>21937.6541172937</v>
       </c>
       <c r="L229" t="n">
-        <v>-0.2</v>
+        <v>-0.14</v>
       </c>
       <c r="M229" t="n">
-        <v>2042.61389019731</v>
+        <v>2110.02889238115</v>
       </c>
       <c r="N229" t="n">
         <v>421.159005233161</v>
@@ -37353,7 +37353,7 @@
         <v>3463.52454615578</v>
       </c>
       <c r="Q229" t="n">
-        <v>5177.74623697901</v>
+        <v>5155.94823697901</v>
       </c>
       <c r="R229" t="n">
         <v>2630.50103083491</v>
@@ -37368,7 +37368,7 @@
         <v>183.205104512052</v>
       </c>
       <c r="V229" t="n">
-        <v>2486.07856234445</v>
+        <v>2472.77956234445</v>
       </c>
       <c r="W229" t="n">
         <v>236.518473484257</v>
@@ -37404,25 +37404,25 @@
         <v>0</v>
       </c>
       <c r="AH229" t="n">
-        <v>2075.98892702443</v>
+        <v>2080.30849834676</v>
       </c>
       <c r="AI229" t="n">
-        <v>346.946674968768</v>
+        <v>349.04455464834</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-3025.71033563014</v>
+        <v>-3015.42757158268</v>
       </c>
       <c r="AK229" t="n">
         <v>-1536.70518949433</v>
       </c>
       <c r="AL229" t="n">
-        <v>-154.35810049771</v>
+        <v>-157.84810049771</v>
       </c>
       <c r="AM229" t="n">
         <v>-71.7641945482261</v>
       </c>
       <c r="AN229" t="n">
-        <v>2219.56881552225</v>
+        <v>2207.59971552225</v>
       </c>
       <c r="AO229" t="n">
         <v>208.360474114872</v>
@@ -37455,10 +37455,10 @@
         <v>0.14805</v>
       </c>
       <c r="AY229" t="n">
-        <v>1831.21705156408</v>
+        <v>1835.02450392963</v>
       </c>
       <c r="AZ229" t="n">
-        <v>309.683357248949</v>
+        <v>311.531986099454</v>
       </c>
     </row>
     <row r="230">
@@ -37496,10 +37496,10 @@
         <v>22144.1209425352</v>
       </c>
       <c r="L230" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="M230" t="n">
-        <v>2052.44350238133</v>
+        <v>2128.26272610237</v>
       </c>
       <c r="N230" t="n">
         <v>424.051302127998</v>
@@ -37511,7 +37511,7 @@
         <v>3492.52886324142</v>
       </c>
       <c r="Q230" t="n">
-        <v>5326.27814367327</v>
+        <v>5304.27594982741</v>
       </c>
       <c r="R230" t="n">
         <v>2656.2474587717</v>
@@ -37526,7 +37526,7 @@
         <v>182.854921256353</v>
       </c>
       <c r="V230" t="n">
-        <v>2542.68376326417</v>
+        <v>2529.07888626417</v>
       </c>
       <c r="W230" t="n">
         <v>239.93696178451</v>
@@ -37562,25 +37562,25 @@
         <v>0</v>
       </c>
       <c r="AH230" t="n">
-        <v>2107.40202266335</v>
+        <v>2111.78726525269</v>
       </c>
       <c r="AI230" t="n">
-        <v>352.119412845882</v>
+        <v>354.248570478128</v>
       </c>
       <c r="AJ230" t="n">
-        <v>-3074.08119197616</v>
+        <v>-3062.45390673909</v>
       </c>
       <c r="AK230" t="n">
         <v>-1551.48029714166</v>
       </c>
       <c r="AL230" t="n">
-        <v>-149.720294657013</v>
+        <v>-153.623627990346</v>
       </c>
       <c r="AM230" t="n">
         <v>-72.0860252567713</v>
       </c>
       <c r="AN230" t="n">
-        <v>2241.97490602891</v>
+        <v>2229.93698370391</v>
       </c>
       <c r="AO230" t="n">
         <v>211.371984516169</v>
@@ -37613,10 +37613,10 @@
         <v>0.124425</v>
       </c>
       <c r="AY230" t="n">
-        <v>1858.92011141979</v>
+        <v>1862.78185323861</v>
       </c>
       <c r="AZ230" t="n">
-        <v>312.631068279413</v>
+        <v>314.505402196127</v>
       </c>
     </row>
     <row r="231">
@@ -37654,10 +37654,10 @@
         <v>22328.3296368604</v>
       </c>
       <c r="L231" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="M231" t="n">
-        <v>2063.8089914691</v>
+        <v>2142.62433392647</v>
       </c>
       <c r="N231" t="n">
         <v>426.972098</v>
@@ -37669,7 +37669,7 @@
         <v>3522.3379634022</v>
       </c>
       <c r="Q231" t="n">
-        <v>5359.1786306302</v>
+        <v>5336.9703301425</v>
       </c>
       <c r="R231" t="n">
         <v>2679.99102251719</v>
@@ -37684,7 +37684,7 @@
         <v>182.181491918471</v>
       </c>
       <c r="V231" t="n">
-        <v>2560.35844805981</v>
+        <v>2546.75357105981</v>
       </c>
       <c r="W231" t="n">
         <v>243.404858750762</v>
@@ -37720,25 +37720,25 @@
         <v>0</v>
       </c>
       <c r="AH231" t="n">
-        <v>2139.30764124513</v>
+        <v>2143.75965743293</v>
       </c>
       <c r="AI231" t="n">
-        <v>357.352066507195</v>
+        <v>359.512864384407</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-3109.84785343304</v>
+        <v>-3096.86345213745</v>
       </c>
       <c r="AK231" t="n">
         <v>-1565.81915799363</v>
       </c>
       <c r="AL231" t="n">
-        <v>-144.247202488968</v>
+        <v>-148.213869155635</v>
       </c>
       <c r="AM231" t="n">
         <v>-72.4720749873869</v>
       </c>
       <c r="AN231" t="n">
-        <v>2264.7861279652</v>
+        <v>2252.6793833152</v>
       </c>
       <c r="AO231" t="n">
         <v>214.42702138253</v>
@@ -37771,10 +37771,10 @@
         <v>0.1008</v>
       </c>
       <c r="AY231" t="n">
-        <v>1885.44368394031</v>
+        <v>1889.36101776006</v>
       </c>
       <c r="AZ231" t="n">
-        <v>315.998201272882</v>
+        <v>317.90085468008</v>
       </c>
     </row>
     <row r="232">
@@ -37884,19 +37884,19 @@
         <v>0</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-2492.79227979258</v>
+        <v>-2482.38801012774</v>
       </c>
       <c r="AK232" t="n">
         <v>-1255.86246022979</v>
       </c>
       <c r="AL232" t="n">
-        <v>-127.893869155635</v>
+        <v>-131.777202488968</v>
       </c>
       <c r="AM232" t="n">
         <v>-66.8020749873869</v>
       </c>
       <c r="AN232" t="n">
-        <v>1707.5521740754</v>
+        <v>1698.4377044254</v>
       </c>
       <c r="AO232" t="n">
         <v>161.968566154394</v>
@@ -37929,10 +37929,10 @@
         <v>0.0819</v>
       </c>
       <c r="AY232" t="n">
-        <v>1422.6071829599</v>
+        <v>1425.56746973229</v>
       </c>
       <c r="AZ232" t="n">
-        <v>237.694084722415</v>
+        <v>239.131347639947</v>
       </c>
     </row>
     <row r="233">
@@ -38042,19 +38042,19 @@
         <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-1868.66510838303</v>
+        <v>-1860.85333674745</v>
       </c>
       <c r="AK233" t="n">
         <v>-942.938109021743</v>
       </c>
       <c r="AL233" t="n">
-        <v>-110.940535822302</v>
+        <v>-114.707202488968</v>
       </c>
       <c r="AM233" t="n">
         <v>-60.9954083207203</v>
       </c>
       <c r="AN233" t="n">
-        <v>1148.1844975479</v>
+        <v>1142.0623028979</v>
       </c>
       <c r="AO233" t="n">
         <v>108.751909620436</v>
@@ -38087,10 +38087,10 @@
         <v>0.063</v>
       </c>
       <c r="AY233" t="n">
-        <v>955.509674379407</v>
+        <v>957.498057604265</v>
       </c>
       <c r="AZ233" t="n">
-        <v>159.631082854442</v>
+        <v>160.59632284407</v>
       </c>
     </row>
     <row r="234">
@@ -38200,19 +38200,19 @@
         <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>-1565.53706442588</v>
+        <v>-1558.99709590278</v>
       </c>
       <c r="AK234" t="n">
         <v>-789.394565505561</v>
       </c>
       <c r="AL234" t="n">
-        <v>-95.3005358223018</v>
+        <v>-97.3805358223018</v>
       </c>
       <c r="AM234" t="n">
         <v>-54.8487416540536</v>
       </c>
       <c r="AN234" t="n">
-        <v>576.080650813456</v>
+        <v>573.019553488456</v>
       </c>
       <c r="AO234" t="n">
         <v>54.7660932189214</v>
@@ -38245,10 +38245,10 @@
         <v>0.0441</v>
       </c>
       <c r="AY234" t="n">
-        <v>481.344219280153</v>
+        <v>482.34592292241</v>
       </c>
       <c r="AZ234" t="n">
-        <v>80.4042149641189</v>
+        <v>80.8903944864916</v>
       </c>
     </row>
     <row r="235">
@@ -38358,7 +38358,7 @@
         <v>0</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-1259.92070157172</v>
+        <v>-1254.66444983981</v>
       </c>
       <c r="AK235" t="n">
         <v>-634.372958132699</v>
@@ -38516,7 +38516,7 @@
         <v>0</v>
       </c>
       <c r="AJ236" t="n">
-        <v>-951.792180676949</v>
+        <v>-947.831671016935</v>
       </c>
       <c r="AK236" t="n">
         <v>-478.004370727428</v>
@@ -38674,7 +38674,7 @@
         <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>-641.127406458208</v>
+        <v>-638.474776798194</v>
       </c>
       <c r="AK237" t="n">
         <v>-320.174308877333</v>
@@ -38832,7 +38832,7 @@
         <v>0</v>
       </c>
       <c r="AJ238" t="n">
-        <v>-321.550717837812</v>
+        <v>-320.21821980855</v>
       </c>
       <c r="AK238" t="n">
         <v>-160.799461351031</v>
